--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>1444693</v>
       </c>
       <c r="B2" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609355.4692097204</v>
+        <v>609355</v>
       </c>
       <c r="R2" t="n">
-        <v>6564546.233256083</v>
+        <v>6564546</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,8 +779,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1444693</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,9 +785,231 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136031607</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110249</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gruvtorp V om , Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>609548</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6564105</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägdike</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136031607</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136031589</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gruvtorp V om , Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>609548</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6564105</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dunker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vägdike</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136031589</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98142</v>
+        <v>98159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110272</v>
+        <v>110274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98159</v>
+        <v>98160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110274</v>
+        <v>110275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98160</v>
+        <v>98161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110275</v>
+        <v>110276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110276</v>
+        <v>110282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98162</v>
+        <v>98168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110282</v>
+        <v>110283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98168</v>
+        <v>98169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110283</v>
+        <v>110294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98169</v>
+        <v>98180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110294</v>
+        <v>110307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98180</v>
+        <v>98193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110307</v>
+        <v>110308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98193</v>
+        <v>98194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110308</v>
+        <v>110321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98194</v>
+        <v>98207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54302-2025 artfynd.xlsx
+++ b/artfynd/A 54302-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>136031607</v>
       </c>
       <c r="B3" t="n">
-        <v>110321</v>
+        <v>110322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136031589</v>
       </c>
       <c r="B4" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
